--- a/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-SVCCoverage.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-05T14:58:51+00:00</t>
+    <t>2024-11-06T10:59:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-SVCCoverage.xlsx
+++ b/r5-ELGA-MOPED-28-Moped-Aufnahme-Bundle-Discriminator-Type-Resource-anpassen/StructureDefinition-SVCCoverage.xlsx
@@ -16,7 +16,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3622" uniqueCount="492">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3622" uniqueCount="493">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2024-11-06T10:59:22+00:00</t>
+    <t>2024-11-06T11:18:03+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -743,35 +743,39 @@
     <t>Coverage.subscriber</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient|http://example.org/StructureDefinition/Hauptversicherter)
+</t>
+  </si>
+  <si>
+    <t>Subscriber to the policy</t>
+  </si>
+  <si>
+    <t>The party who has signed-up for or 'owns' the contractual relationship to the policy or to whom the benefit of the policy for services rendered to them or their family is due.</t>
+  </si>
+  <si>
+    <t>May be self or a parent in the case of dependants. A subscriber is only required on certain types of policies not all policies and that it is appropriate to have just a policyholder and a beneficiary when not other party can join that policy instance.</t>
+  </si>
+  <si>
+    <t>This is the party who is entitled to the benfits under the policy.</t>
+  </si>
+  <si>
+    <t>Coverage.subscriberId</t>
+  </si>
+  <si>
+    <t>ID assigned to the subscriber</t>
+  </si>
+  <si>
+    <t>The insurer assigned ID for the Subscriber.</t>
+  </si>
+  <si>
+    <t>The insurer requires this identifier on correspondance and claims (digital and otherwise).</t>
+  </si>
+  <si>
+    <t>Coverage.beneficiary</t>
+  </si>
+  <si>
     <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/5.0.0/StructureDefinition/at-core-patient)
 </t>
-  </si>
-  <si>
-    <t>Subscriber to the policy</t>
-  </si>
-  <si>
-    <t>The party who has signed-up for or 'owns' the contractual relationship to the policy or to whom the benefit of the policy for services rendered to them or their family is due.</t>
-  </si>
-  <si>
-    <t>May be self or a parent in the case of dependants. A subscriber is only required on certain types of policies not all policies and that it is appropriate to have just a policyholder and a beneficiary when not other party can join that policy instance.</t>
-  </si>
-  <si>
-    <t>This is the party who is entitled to the benfits under the policy.</t>
-  </si>
-  <si>
-    <t>Coverage.subscriberId</t>
-  </si>
-  <si>
-    <t>ID assigned to the subscriber</t>
-  </si>
-  <si>
-    <t>The insurer assigned ID for the Subscriber.</t>
-  </si>
-  <si>
-    <t>The insurer requires this identifier on correspondance and claims (digital and otherwise).</t>
-  </si>
-  <si>
-    <t>Coverage.beneficiary</t>
   </si>
   <si>
     <t>Plan beneficiary</t>
@@ -1863,7 +1867,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="81.6328125" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="134.72265625" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
@@ -4926,17 +4930,17 @@
         <v>90</v>
       </c>
       <c r="K26" t="s" s="2">
-        <v>231</v>
+        <v>241</v>
       </c>
       <c r="L26" t="s" s="2">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="M26" t="s" s="2">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="N26" s="2"/>
       <c r="O26" t="s" s="2">
-        <v>243</v>
+        <v>244</v>
       </c>
       <c r="P26" t="s" s="2">
         <v>19</v>
@@ -5000,7 +5004,7 @@
         <v>101</v>
       </c>
       <c r="AK26" t="s" s="2">
-        <v>244</v>
+        <v>245</v>
       </c>
       <c r="AL26" t="s" s="2">
         <v>226</v>
@@ -5020,10 +5024,10 @@
     </row>
     <row r="27" hidden="true">
       <c r="A27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="B27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="C27" s="2"/>
       <c r="D27" t="s" s="2">
@@ -5049,16 +5053,16 @@
         <v>191</v>
       </c>
       <c r="L27" t="s" s="2">
-        <v>246</v>
+        <v>247</v>
       </c>
       <c r="M27" t="s" s="2">
-        <v>247</v>
+        <v>248</v>
       </c>
       <c r="N27" t="s" s="2">
-        <v>248</v>
+        <v>249</v>
       </c>
       <c r="O27" t="s" s="2">
-        <v>249</v>
+        <v>250</v>
       </c>
       <c r="P27" t="s" s="2">
         <v>19</v>
@@ -5107,7 +5111,7 @@
         <v>19</v>
       </c>
       <c r="AF27" t="s" s="2">
-        <v>245</v>
+        <v>246</v>
       </c>
       <c r="AG27" t="s" s="2">
         <v>78</v>
@@ -5131,21 +5135,21 @@
         <v>19</v>
       </c>
       <c r="AN27" t="s" s="2">
-        <v>250</v>
+        <v>251</v>
       </c>
       <c r="AO27" t="s" s="2">
         <v>19</v>
       </c>
       <c r="AP27" t="s" s="2">
-        <v>251</v>
+        <v>252</v>
       </c>
     </row>
     <row r="28" hidden="true">
       <c r="A28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="B28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="C28" s="2"/>
       <c r="D28" t="s" s="2">
@@ -5171,16 +5175,16 @@
         <v>214</v>
       </c>
       <c r="L28" t="s" s="2">
-        <v>253</v>
+        <v>254</v>
       </c>
       <c r="M28" t="s" s="2">
-        <v>254</v>
+        <v>255</v>
       </c>
       <c r="N28" t="s" s="2">
-        <v>255</v>
+        <v>256</v>
       </c>
       <c r="O28" t="s" s="2">
-        <v>256</v>
+        <v>257</v>
       </c>
       <c r="P28" t="s" s="2">
         <v>19</v>
@@ -5205,13 +5209,13 @@
         <v>19</v>
       </c>
       <c r="X28" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y28" t="s" s="2">
-        <v>258</v>
+        <v>259</v>
       </c>
       <c r="Z28" t="s" s="2">
-        <v>259</v>
+        <v>260</v>
       </c>
       <c r="AA28" t="s" s="2">
         <v>19</v>
@@ -5229,7 +5233,7 @@
         <v>19</v>
       </c>
       <c r="AF28" t="s" s="2">
-        <v>252</v>
+        <v>253</v>
       </c>
       <c r="AG28" t="s" s="2">
         <v>78</v>
@@ -5253,7 +5257,7 @@
         <v>19</v>
       </c>
       <c r="AN28" t="s" s="2">
-        <v>260</v>
+        <v>261</v>
       </c>
       <c r="AO28" t="s" s="2">
         <v>19</v>
@@ -5264,10 +5268,10 @@
     </row>
     <row r="29" hidden="true">
       <c r="A29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="B29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="C29" s="2"/>
       <c r="D29" t="s" s="2">
@@ -5290,17 +5294,17 @@
         <v>90</v>
       </c>
       <c r="K29" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L29" t="s" s="2">
-        <v>263</v>
+        <v>264</v>
       </c>
       <c r="M29" t="s" s="2">
-        <v>264</v>
+        <v>265</v>
       </c>
       <c r="N29" s="2"/>
       <c r="O29" t="s" s="2">
-        <v>265</v>
+        <v>266</v>
       </c>
       <c r="P29" t="s" s="2">
         <v>19</v>
@@ -5349,7 +5353,7 @@
         <v>19</v>
       </c>
       <c r="AF29" t="s" s="2">
-        <v>261</v>
+        <v>262</v>
       </c>
       <c r="AG29" t="s" s="2">
         <v>78</v>
@@ -5364,13 +5368,13 @@
         <v>101</v>
       </c>
       <c r="AK29" t="s" s="2">
-        <v>266</v>
+        <v>267</v>
       </c>
       <c r="AL29" t="s" s="2">
-        <v>267</v>
+        <v>268</v>
       </c>
       <c r="AM29" t="s" s="2">
-        <v>268</v>
+        <v>269</v>
       </c>
       <c r="AN29" t="s" s="2">
         <v>19</v>
@@ -5379,15 +5383,15 @@
         <v>19</v>
       </c>
       <c r="AP29" t="s" s="2">
-        <v>269</v>
+        <v>270</v>
       </c>
     </row>
     <row r="30" hidden="true">
       <c r="A30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="B30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="C30" s="2"/>
       <c r="D30" t="s" s="2">
@@ -5410,19 +5414,19 @@
         <v>90</v>
       </c>
       <c r="K30" t="s" s="2">
-        <v>271</v>
+        <v>272</v>
       </c>
       <c r="L30" t="s" s="2">
-        <v>272</v>
+        <v>273</v>
       </c>
       <c r="M30" t="s" s="2">
-        <v>273</v>
+        <v>274</v>
       </c>
       <c r="N30" t="s" s="2">
-        <v>274</v>
+        <v>275</v>
       </c>
       <c r="O30" t="s" s="2">
-        <v>275</v>
+        <v>276</v>
       </c>
       <c r="P30" t="s" s="2">
         <v>19</v>
@@ -5471,7 +5475,7 @@
         <v>19</v>
       </c>
       <c r="AF30" t="s" s="2">
-        <v>270</v>
+        <v>271</v>
       </c>
       <c r="AG30" t="s" s="2">
         <v>78</v>
@@ -5506,10 +5510,10 @@
     </row>
     <row r="31" hidden="true">
       <c r="A31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="B31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C31" s="2"/>
       <c r="D31" t="s" s="2">
@@ -5535,16 +5539,16 @@
         <v>187</v>
       </c>
       <c r="L31" t="s" s="2">
-        <v>277</v>
+        <v>278</v>
       </c>
       <c r="M31" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N31" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O31" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P31" t="s" s="2">
         <v>19</v>
@@ -5581,7 +5585,7 @@
         <v>19</v>
       </c>
       <c r="AB31" t="s" s="2">
-        <v>281</v>
+        <v>282</v>
       </c>
       <c r="AC31" s="2"/>
       <c r="AD31" t="s" s="2">
@@ -5591,7 +5595,7 @@
         <v>140</v>
       </c>
       <c r="AF31" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG31" t="s" s="2">
         <v>78</v>
@@ -5626,10 +5630,10 @@
     </row>
     <row r="32" hidden="true">
       <c r="A32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="B32" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C32" s="2"/>
       <c r="D32" t="s" s="2">
@@ -5744,10 +5748,10 @@
     </row>
     <row r="33" hidden="true">
       <c r="A33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="B33" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C33" s="2"/>
       <c r="D33" t="s" s="2">
@@ -5864,10 +5868,10 @@
     </row>
     <row r="34" hidden="true">
       <c r="A34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="B34" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C34" s="2"/>
       <c r="D34" t="s" s="2">
@@ -5986,10 +5990,10 @@
     </row>
     <row r="35" hidden="true">
       <c r="A35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="B35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C35" s="2"/>
       <c r="D35" t="s" s="2">
@@ -6015,14 +6019,14 @@
         <v>214</v>
       </c>
       <c r="L35" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M35" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N35" s="2"/>
       <c r="O35" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P35" t="s" s="2">
         <v>19</v>
@@ -6047,13 +6051,13 @@
         <v>19</v>
       </c>
       <c r="X35" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y35" t="s" s="2">
-        <v>289</v>
+        <v>290</v>
       </c>
       <c r="Z35" t="s" s="2">
-        <v>290</v>
+        <v>291</v>
       </c>
       <c r="AA35" t="s" s="2">
         <v>19</v>
@@ -6071,7 +6075,7 @@
         <v>19</v>
       </c>
       <c r="AF35" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG35" t="s" s="2">
         <v>89</v>
@@ -6106,10 +6110,10 @@
     </row>
     <row r="36" hidden="true">
       <c r="A36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="B36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C36" s="2"/>
       <c r="D36" t="s" s="2">
@@ -6135,16 +6139,16 @@
         <v>161</v>
       </c>
       <c r="L36" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M36" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N36" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O36" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P36" t="s" s="2">
         <v>19</v>
@@ -6193,7 +6197,7 @@
         <v>19</v>
       </c>
       <c r="AF36" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG36" t="s" s="2">
         <v>89</v>
@@ -6217,21 +6221,21 @@
         <v>19</v>
       </c>
       <c r="AN36" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO36" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP36" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="37" hidden="true">
       <c r="A37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="B37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C37" s="2"/>
       <c r="D37" t="s" s="2">
@@ -6257,14 +6261,14 @@
         <v>191</v>
       </c>
       <c r="L37" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M37" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N37" s="2"/>
       <c r="O37" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P37" t="s" s="2">
         <v>19</v>
@@ -6313,7 +6317,7 @@
         <v>19</v>
       </c>
       <c r="AF37" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG37" t="s" s="2">
         <v>78</v>
@@ -6337,24 +6341,24 @@
         <v>19</v>
       </c>
       <c r="AN37" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO37" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP37" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="38" hidden="true">
       <c r="A38" t="s" s="2">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="B38" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="D38" t="s" s="2">
         <v>19</v>
@@ -6379,16 +6383,16 @@
         <v>187</v>
       </c>
       <c r="L38" t="s" s="2">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="M38" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N38" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O38" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P38" t="s" s="2">
         <v>19</v>
@@ -6437,7 +6441,7 @@
         <v>19</v>
       </c>
       <c r="AF38" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG38" t="s" s="2">
         <v>78</v>
@@ -6472,10 +6476,10 @@
     </row>
     <row r="39" hidden="true">
       <c r="A39" t="s" s="2">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="B39" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C39" s="2"/>
       <c r="D39" t="s" s="2">
@@ -6590,10 +6594,10 @@
     </row>
     <row r="40" hidden="true">
       <c r="A40" t="s" s="2">
-        <v>307</v>
+        <v>308</v>
       </c>
       <c r="B40" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C40" s="2"/>
       <c r="D40" t="s" s="2">
@@ -6710,10 +6714,10 @@
     </row>
     <row r="41" hidden="true">
       <c r="A41" t="s" s="2">
-        <v>308</v>
+        <v>309</v>
       </c>
       <c r="B41" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C41" s="2"/>
       <c r="D41" t="s" s="2">
@@ -6832,10 +6836,10 @@
     </row>
     <row r="42" hidden="true">
       <c r="A42" t="s" s="2">
-        <v>309</v>
+        <v>310</v>
       </c>
       <c r="B42" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C42" s="2"/>
       <c r="D42" t="s" s="2">
@@ -6861,14 +6865,14 @@
         <v>214</v>
       </c>
       <c r="L42" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M42" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N42" s="2"/>
       <c r="O42" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P42" t="s" s="2">
         <v>19</v>
@@ -6897,7 +6901,7 @@
       </c>
       <c r="Y42" s="2"/>
       <c r="Z42" t="s" s="2">
-        <v>310</v>
+        <v>311</v>
       </c>
       <c r="AA42" t="s" s="2">
         <v>19</v>
@@ -6915,7 +6919,7 @@
         <v>19</v>
       </c>
       <c r="AF42" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG42" t="s" s="2">
         <v>89</v>
@@ -6950,10 +6954,10 @@
     </row>
     <row r="43" hidden="true">
       <c r="A43" t="s" s="2">
-        <v>311</v>
+        <v>312</v>
       </c>
       <c r="B43" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C43" s="2"/>
       <c r="D43" t="s" s="2">
@@ -7068,10 +7072,10 @@
     </row>
     <row r="44" hidden="true">
       <c r="A44" t="s" s="2">
-        <v>313</v>
+        <v>314</v>
       </c>
       <c r="B44" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C44" s="2"/>
       <c r="D44" t="s" s="2">
@@ -7144,7 +7148,7 @@
         <v>139</v>
       </c>
       <c r="AC44" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AD44" t="s" s="2">
         <v>19</v>
@@ -7188,10 +7192,10 @@
     </row>
     <row r="45" hidden="true">
       <c r="A45" t="s" s="2">
-        <v>316</v>
+        <v>317</v>
       </c>
       <c r="B45" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C45" s="2"/>
       <c r="D45" t="s" s="2">
@@ -7214,19 +7218,19 @@
         <v>90</v>
       </c>
       <c r="K45" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L45" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M45" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N45" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O45" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P45" t="s" s="2">
         <v>19</v>
@@ -7275,7 +7279,7 @@
         <v>19</v>
       </c>
       <c r="AF45" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG45" t="s" s="2">
         <v>78</v>
@@ -7296,7 +7300,7 @@
         <v>19</v>
       </c>
       <c r="AM45" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN45" t="s" s="2">
         <v>19</v>
@@ -7305,15 +7309,15 @@
         <v>19</v>
       </c>
       <c r="AP45" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="46" hidden="true">
       <c r="A46" t="s" s="2">
-        <v>326</v>
+        <v>327</v>
       </c>
       <c r="B46" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C46" s="2"/>
       <c r="D46" t="s" s="2">
@@ -7428,10 +7432,10 @@
     </row>
     <row r="47" hidden="true">
       <c r="A47" t="s" s="2">
-        <v>328</v>
+        <v>329</v>
       </c>
       <c r="B47" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C47" s="2"/>
       <c r="D47" t="s" s="2">
@@ -7504,7 +7508,7 @@
         <v>139</v>
       </c>
       <c r="AC47" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AD47" t="s" s="2">
         <v>19</v>
@@ -7548,10 +7552,10 @@
     </row>
     <row r="48" hidden="true">
       <c r="A48" t="s" s="2">
-        <v>330</v>
+        <v>331</v>
       </c>
       <c r="B48" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C48" s="2"/>
       <c r="D48" t="s" s="2">
@@ -7577,16 +7581,16 @@
         <v>103</v>
       </c>
       <c r="L48" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M48" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N48" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O48" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P48" t="s" s="2">
         <v>19</v>
@@ -7596,7 +7600,7 @@
         <v>19</v>
       </c>
       <c r="S48" t="s" s="2">
-        <v>336</v>
+        <v>337</v>
       </c>
       <c r="T48" t="s" s="2">
         <v>19</v>
@@ -7635,7 +7639,7 @@
         <v>19</v>
       </c>
       <c r="AF48" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG48" t="s" s="2">
         <v>78</v>
@@ -7656,7 +7660,7 @@
         <v>19</v>
       </c>
       <c r="AM48" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN48" t="s" s="2">
         <v>19</v>
@@ -7665,15 +7669,15 @@
         <v>19</v>
       </c>
       <c r="AP48" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="49" hidden="true">
       <c r="A49" t="s" s="2">
-        <v>340</v>
+        <v>341</v>
       </c>
       <c r="B49" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C49" s="2"/>
       <c r="D49" t="s" s="2">
@@ -7699,13 +7703,13 @@
         <v>191</v>
       </c>
       <c r="L49" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M49" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N49" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O49" s="2"/>
       <c r="P49" t="s" s="2">
@@ -7755,7 +7759,7 @@
         <v>19</v>
       </c>
       <c r="AF49" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG49" t="s" s="2">
         <v>78</v>
@@ -7776,7 +7780,7 @@
         <v>19</v>
       </c>
       <c r="AM49" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN49" t="s" s="2">
         <v>19</v>
@@ -7785,15 +7789,15 @@
         <v>19</v>
       </c>
       <c r="AP49" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="50" hidden="true">
       <c r="A50" t="s" s="2">
-        <v>348</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C50" s="2"/>
       <c r="D50" t="s" s="2">
@@ -7819,14 +7823,14 @@
         <v>109</v>
       </c>
       <c r="L50" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M50" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N50" s="2"/>
       <c r="O50" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P50" t="s" s="2">
         <v>19</v>
@@ -7875,7 +7879,7 @@
         <v>19</v>
       </c>
       <c r="AF50" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG50" t="s" s="2">
         <v>78</v>
@@ -7884,7 +7888,7 @@
         <v>89</v>
       </c>
       <c r="AI50" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AJ50" t="s" s="2">
         <v>101</v>
@@ -7896,7 +7900,7 @@
         <v>19</v>
       </c>
       <c r="AM50" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN50" t="s" s="2">
         <v>19</v>
@@ -7905,15 +7909,15 @@
         <v>19</v>
       </c>
       <c r="AP50" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="51" hidden="true">
       <c r="A51" t="s" s="2">
-        <v>357</v>
+        <v>358</v>
       </c>
       <c r="B51" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C51" s="2"/>
       <c r="D51" t="s" s="2">
@@ -7939,14 +7943,14 @@
         <v>191</v>
       </c>
       <c r="L51" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M51" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N51" s="2"/>
       <c r="O51" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P51" t="s" s="2">
         <v>19</v>
@@ -7995,7 +7999,7 @@
         <v>19</v>
       </c>
       <c r="AF51" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG51" t="s" s="2">
         <v>78</v>
@@ -8004,7 +8008,7 @@
         <v>89</v>
       </c>
       <c r="AI51" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AJ51" t="s" s="2">
         <v>101</v>
@@ -8016,7 +8020,7 @@
         <v>19</v>
       </c>
       <c r="AM51" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN51" t="s" s="2">
         <v>19</v>
@@ -8025,15 +8029,15 @@
         <v>19</v>
       </c>
       <c r="AP51" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="52" hidden="true">
       <c r="A52" t="s" s="2">
-        <v>365</v>
+        <v>366</v>
       </c>
       <c r="B52" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C52" s="2"/>
       <c r="D52" t="s" s="2">
@@ -8056,19 +8060,19 @@
         <v>90</v>
       </c>
       <c r="K52" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L52" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M52" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N52" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O52" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P52" t="s" s="2">
         <v>19</v>
@@ -8117,7 +8121,7 @@
         <v>19</v>
       </c>
       <c r="AF52" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG52" t="s" s="2">
         <v>78</v>
@@ -8138,7 +8142,7 @@
         <v>19</v>
       </c>
       <c r="AM52" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN52" t="s" s="2">
         <v>19</v>
@@ -8147,15 +8151,15 @@
         <v>19</v>
       </c>
       <c r="AP52" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="53" hidden="true">
       <c r="A53" t="s" s="2">
-        <v>375</v>
+        <v>376</v>
       </c>
       <c r="B53" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C53" s="2"/>
       <c r="D53" t="s" s="2">
@@ -8181,16 +8185,16 @@
         <v>191</v>
       </c>
       <c r="L53" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M53" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N53" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O53" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P53" t="s" s="2">
         <v>19</v>
@@ -8239,7 +8243,7 @@
         <v>19</v>
       </c>
       <c r="AF53" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG53" t="s" s="2">
         <v>78</v>
@@ -8260,7 +8264,7 @@
         <v>19</v>
       </c>
       <c r="AM53" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN53" t="s" s="2">
         <v>19</v>
@@ -8269,15 +8273,15 @@
         <v>19</v>
       </c>
       <c r="AP53" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="54" hidden="true">
       <c r="A54" t="s" s="2">
-        <v>384</v>
+        <v>385</v>
       </c>
       <c r="B54" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C54" s="2"/>
       <c r="D54" t="s" s="2">
@@ -8303,16 +8307,16 @@
         <v>161</v>
       </c>
       <c r="L54" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M54" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N54" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O54" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P54" t="s" s="2">
         <v>19</v>
@@ -8361,7 +8365,7 @@
         <v>19</v>
       </c>
       <c r="AF54" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG54" t="s" s="2">
         <v>89</v>
@@ -8385,21 +8389,21 @@
         <v>19</v>
       </c>
       <c r="AN54" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO54" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP54" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="55" hidden="true">
       <c r="A55" t="s" s="2">
-        <v>385</v>
+        <v>386</v>
       </c>
       <c r="B55" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C55" s="2"/>
       <c r="D55" t="s" s="2">
@@ -8425,14 +8429,14 @@
         <v>191</v>
       </c>
       <c r="L55" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M55" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N55" s="2"/>
       <c r="O55" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P55" t="s" s="2">
         <v>19</v>
@@ -8481,7 +8485,7 @@
         <v>19</v>
       </c>
       <c r="AF55" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG55" t="s" s="2">
         <v>78</v>
@@ -8505,24 +8509,24 @@
         <v>19</v>
       </c>
       <c r="AN55" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO55" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP55" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="56" hidden="true">
       <c r="A56" t="s" s="2">
-        <v>386</v>
+        <v>387</v>
       </c>
       <c r="B56" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="C56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="D56" t="s" s="2">
         <v>19</v>
@@ -8547,16 +8551,16 @@
         <v>187</v>
       </c>
       <c r="L56" t="s" s="2">
-        <v>387</v>
+        <v>388</v>
       </c>
       <c r="M56" t="s" s="2">
-        <v>278</v>
+        <v>279</v>
       </c>
       <c r="N56" t="s" s="2">
-        <v>279</v>
+        <v>280</v>
       </c>
       <c r="O56" t="s" s="2">
-        <v>280</v>
+        <v>281</v>
       </c>
       <c r="P56" t="s" s="2">
         <v>19</v>
@@ -8605,7 +8609,7 @@
         <v>19</v>
       </c>
       <c r="AF56" t="s" s="2">
-        <v>276</v>
+        <v>277</v>
       </c>
       <c r="AG56" t="s" s="2">
         <v>78</v>
@@ -8640,10 +8644,10 @@
     </row>
     <row r="57" hidden="true">
       <c r="A57" t="s" s="2">
-        <v>388</v>
+        <v>389</v>
       </c>
       <c r="B57" t="s" s="2">
-        <v>282</v>
+        <v>283</v>
       </c>
       <c r="C57" s="2"/>
       <c r="D57" t="s" s="2">
@@ -8758,10 +8762,10 @@
     </row>
     <row r="58" hidden="true">
       <c r="A58" t="s" s="2">
-        <v>389</v>
+        <v>390</v>
       </c>
       <c r="B58" t="s" s="2">
-        <v>283</v>
+        <v>284</v>
       </c>
       <c r="C58" s="2"/>
       <c r="D58" t="s" s="2">
@@ -8878,10 +8882,10 @@
     </row>
     <row r="59" hidden="true">
       <c r="A59" t="s" s="2">
-        <v>390</v>
+        <v>391</v>
       </c>
       <c r="B59" t="s" s="2">
-        <v>284</v>
+        <v>285</v>
       </c>
       <c r="C59" s="2"/>
       <c r="D59" t="s" s="2">
@@ -9000,10 +9004,10 @@
     </row>
     <row r="60" hidden="true">
       <c r="A60" t="s" s="2">
-        <v>391</v>
+        <v>392</v>
       </c>
       <c r="B60" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="C60" s="2"/>
       <c r="D60" t="s" s="2">
@@ -9029,14 +9033,14 @@
         <v>214</v>
       </c>
       <c r="L60" t="s" s="2">
-        <v>286</v>
+        <v>287</v>
       </c>
       <c r="M60" t="s" s="2">
-        <v>287</v>
+        <v>288</v>
       </c>
       <c r="N60" s="2"/>
       <c r="O60" t="s" s="2">
-        <v>288</v>
+        <v>289</v>
       </c>
       <c r="P60" t="s" s="2">
         <v>19</v>
@@ -9065,7 +9069,7 @@
       </c>
       <c r="Y60" s="2"/>
       <c r="Z60" t="s" s="2">
-        <v>392</v>
+        <v>393</v>
       </c>
       <c r="AA60" t="s" s="2">
         <v>19</v>
@@ -9083,7 +9087,7 @@
         <v>19</v>
       </c>
       <c r="AF60" t="s" s="2">
-        <v>285</v>
+        <v>286</v>
       </c>
       <c r="AG60" t="s" s="2">
         <v>89</v>
@@ -9118,10 +9122,10 @@
     </row>
     <row r="61" hidden="true">
       <c r="A61" t="s" s="2">
-        <v>393</v>
+        <v>394</v>
       </c>
       <c r="B61" t="s" s="2">
-        <v>312</v>
+        <v>313</v>
       </c>
       <c r="C61" s="2"/>
       <c r="D61" t="s" s="2">
@@ -9236,10 +9240,10 @@
     </row>
     <row r="62" hidden="true">
       <c r="A62" t="s" s="2">
-        <v>394</v>
+        <v>395</v>
       </c>
       <c r="B62" t="s" s="2">
-        <v>314</v>
+        <v>315</v>
       </c>
       <c r="C62" s="2"/>
       <c r="D62" t="s" s="2">
@@ -9312,7 +9316,7 @@
         <v>139</v>
       </c>
       <c r="AC62" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AD62" t="s" s="2">
         <v>19</v>
@@ -9356,10 +9360,10 @@
     </row>
     <row r="63" hidden="true">
       <c r="A63" t="s" s="2">
-        <v>395</v>
+        <v>396</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>317</v>
+        <v>318</v>
       </c>
       <c r="C63" s="2"/>
       <c r="D63" t="s" s="2">
@@ -9382,19 +9386,19 @@
         <v>90</v>
       </c>
       <c r="K63" t="s" s="2">
-        <v>318</v>
+        <v>319</v>
       </c>
       <c r="L63" t="s" s="2">
-        <v>319</v>
+        <v>320</v>
       </c>
       <c r="M63" t="s" s="2">
-        <v>320</v>
+        <v>321</v>
       </c>
       <c r="N63" t="s" s="2">
-        <v>321</v>
+        <v>322</v>
       </c>
       <c r="O63" t="s" s="2">
-        <v>322</v>
+        <v>323</v>
       </c>
       <c r="P63" t="s" s="2">
         <v>19</v>
@@ -9443,7 +9447,7 @@
         <v>19</v>
       </c>
       <c r="AF63" t="s" s="2">
-        <v>323</v>
+        <v>324</v>
       </c>
       <c r="AG63" t="s" s="2">
         <v>78</v>
@@ -9464,7 +9468,7 @@
         <v>19</v>
       </c>
       <c r="AM63" t="s" s="2">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="AN63" t="s" s="2">
         <v>19</v>
@@ -9473,15 +9477,15 @@
         <v>19</v>
       </c>
       <c r="AP63" t="s" s="2">
-        <v>325</v>
+        <v>326</v>
       </c>
     </row>
     <row r="64" hidden="true">
       <c r="A64" t="s" s="2">
-        <v>396</v>
+        <v>397</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>327</v>
+        <v>328</v>
       </c>
       <c r="C64" s="2"/>
       <c r="D64" t="s" s="2">
@@ -9596,10 +9600,10 @@
     </row>
     <row r="65" hidden="true">
       <c r="A65" t="s" s="2">
-        <v>397</v>
+        <v>398</v>
       </c>
       <c r="B65" t="s" s="2">
-        <v>329</v>
+        <v>330</v>
       </c>
       <c r="C65" s="2"/>
       <c r="D65" t="s" s="2">
@@ -9672,7 +9676,7 @@
         <v>139</v>
       </c>
       <c r="AC65" t="s" s="2">
-        <v>315</v>
+        <v>316</v>
       </c>
       <c r="AD65" t="s" s="2">
         <v>19</v>
@@ -9716,10 +9720,10 @@
     </row>
     <row r="66" hidden="true">
       <c r="A66" t="s" s="2">
-        <v>398</v>
+        <v>399</v>
       </c>
       <c r="B66" t="s" s="2">
-        <v>331</v>
+        <v>332</v>
       </c>
       <c r="C66" s="2"/>
       <c r="D66" t="s" s="2">
@@ -9745,16 +9749,16 @@
         <v>103</v>
       </c>
       <c r="L66" t="s" s="2">
-        <v>332</v>
+        <v>333</v>
       </c>
       <c r="M66" t="s" s="2">
-        <v>333</v>
+        <v>334</v>
       </c>
       <c r="N66" t="s" s="2">
-        <v>334</v>
+        <v>335</v>
       </c>
       <c r="O66" t="s" s="2">
-        <v>335</v>
+        <v>336</v>
       </c>
       <c r="P66" t="s" s="2">
         <v>19</v>
@@ -9764,7 +9768,7 @@
         <v>19</v>
       </c>
       <c r="S66" t="s" s="2">
-        <v>399</v>
+        <v>400</v>
       </c>
       <c r="T66" t="s" s="2">
         <v>19</v>
@@ -9803,7 +9807,7 @@
         <v>19</v>
       </c>
       <c r="AF66" t="s" s="2">
-        <v>337</v>
+        <v>338</v>
       </c>
       <c r="AG66" t="s" s="2">
         <v>78</v>
@@ -9824,7 +9828,7 @@
         <v>19</v>
       </c>
       <c r="AM66" t="s" s="2">
-        <v>338</v>
+        <v>339</v>
       </c>
       <c r="AN66" t="s" s="2">
         <v>19</v>
@@ -9833,15 +9837,15 @@
         <v>19</v>
       </c>
       <c r="AP66" t="s" s="2">
-        <v>339</v>
+        <v>340</v>
       </c>
     </row>
     <row r="67" hidden="true">
       <c r="A67" t="s" s="2">
-        <v>400</v>
+        <v>401</v>
       </c>
       <c r="B67" t="s" s="2">
-        <v>341</v>
+        <v>342</v>
       </c>
       <c r="C67" s="2"/>
       <c r="D67" t="s" s="2">
@@ -9867,13 +9871,13 @@
         <v>191</v>
       </c>
       <c r="L67" t="s" s="2">
-        <v>342</v>
+        <v>343</v>
       </c>
       <c r="M67" t="s" s="2">
-        <v>343</v>
+        <v>344</v>
       </c>
       <c r="N67" t="s" s="2">
-        <v>344</v>
+        <v>345</v>
       </c>
       <c r="O67" s="2"/>
       <c r="P67" t="s" s="2">
@@ -9923,7 +9927,7 @@
         <v>19</v>
       </c>
       <c r="AF67" t="s" s="2">
-        <v>345</v>
+        <v>346</v>
       </c>
       <c r="AG67" t="s" s="2">
         <v>78</v>
@@ -9944,7 +9948,7 @@
         <v>19</v>
       </c>
       <c r="AM67" t="s" s="2">
-        <v>346</v>
+        <v>347</v>
       </c>
       <c r="AN67" t="s" s="2">
         <v>19</v>
@@ -9953,15 +9957,15 @@
         <v>19</v>
       </c>
       <c r="AP67" t="s" s="2">
-        <v>347</v>
+        <v>348</v>
       </c>
     </row>
     <row r="68" hidden="true">
       <c r="A68" t="s" s="2">
-        <v>401</v>
+        <v>402</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>349</v>
+        <v>350</v>
       </c>
       <c r="C68" s="2"/>
       <c r="D68" t="s" s="2">
@@ -9987,14 +9991,14 @@
         <v>109</v>
       </c>
       <c r="L68" t="s" s="2">
-        <v>350</v>
+        <v>351</v>
       </c>
       <c r="M68" t="s" s="2">
-        <v>351</v>
+        <v>352</v>
       </c>
       <c r="N68" s="2"/>
       <c r="O68" t="s" s="2">
-        <v>352</v>
+        <v>353</v>
       </c>
       <c r="P68" t="s" s="2">
         <v>19</v>
@@ -10043,7 +10047,7 @@
         <v>19</v>
       </c>
       <c r="AF68" t="s" s="2">
-        <v>353</v>
+        <v>354</v>
       </c>
       <c r="AG68" t="s" s="2">
         <v>78</v>
@@ -10052,7 +10056,7 @@
         <v>89</v>
       </c>
       <c r="AI68" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AJ68" t="s" s="2">
         <v>101</v>
@@ -10064,7 +10068,7 @@
         <v>19</v>
       </c>
       <c r="AM68" t="s" s="2">
-        <v>355</v>
+        <v>356</v>
       </c>
       <c r="AN68" t="s" s="2">
         <v>19</v>
@@ -10073,15 +10077,15 @@
         <v>19</v>
       </c>
       <c r="AP68" t="s" s="2">
-        <v>356</v>
+        <v>357</v>
       </c>
     </row>
     <row r="69" hidden="true">
       <c r="A69" t="s" s="2">
-        <v>402</v>
+        <v>403</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>358</v>
+        <v>359</v>
       </c>
       <c r="C69" s="2"/>
       <c r="D69" t="s" s="2">
@@ -10107,14 +10111,14 @@
         <v>191</v>
       </c>
       <c r="L69" t="s" s="2">
-        <v>359</v>
+        <v>360</v>
       </c>
       <c r="M69" t="s" s="2">
-        <v>360</v>
+        <v>361</v>
       </c>
       <c r="N69" s="2"/>
       <c r="O69" t="s" s="2">
-        <v>361</v>
+        <v>362</v>
       </c>
       <c r="P69" t="s" s="2">
         <v>19</v>
@@ -10163,7 +10167,7 @@
         <v>19</v>
       </c>
       <c r="AF69" t="s" s="2">
-        <v>362</v>
+        <v>363</v>
       </c>
       <c r="AG69" t="s" s="2">
         <v>78</v>
@@ -10172,7 +10176,7 @@
         <v>89</v>
       </c>
       <c r="AI69" t="s" s="2">
-        <v>354</v>
+        <v>355</v>
       </c>
       <c r="AJ69" t="s" s="2">
         <v>101</v>
@@ -10184,7 +10188,7 @@
         <v>19</v>
       </c>
       <c r="AM69" t="s" s="2">
-        <v>363</v>
+        <v>364</v>
       </c>
       <c r="AN69" t="s" s="2">
         <v>19</v>
@@ -10193,15 +10197,15 @@
         <v>19</v>
       </c>
       <c r="AP69" t="s" s="2">
-        <v>364</v>
+        <v>365</v>
       </c>
     </row>
     <row r="70" hidden="true">
       <c r="A70" t="s" s="2">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="B70" t="s" s="2">
-        <v>366</v>
+        <v>367</v>
       </c>
       <c r="C70" s="2"/>
       <c r="D70" t="s" s="2">
@@ -10224,19 +10228,19 @@
         <v>90</v>
       </c>
       <c r="K70" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L70" t="s" s="2">
-        <v>368</v>
+        <v>369</v>
       </c>
       <c r="M70" t="s" s="2">
-        <v>369</v>
+        <v>370</v>
       </c>
       <c r="N70" t="s" s="2">
-        <v>370</v>
+        <v>371</v>
       </c>
       <c r="O70" t="s" s="2">
-        <v>371</v>
+        <v>372</v>
       </c>
       <c r="P70" t="s" s="2">
         <v>19</v>
@@ -10285,7 +10289,7 @@
         <v>19</v>
       </c>
       <c r="AF70" t="s" s="2">
-        <v>372</v>
+        <v>373</v>
       </c>
       <c r="AG70" t="s" s="2">
         <v>78</v>
@@ -10306,7 +10310,7 @@
         <v>19</v>
       </c>
       <c r="AM70" t="s" s="2">
-        <v>373</v>
+        <v>374</v>
       </c>
       <c r="AN70" t="s" s="2">
         <v>19</v>
@@ -10315,15 +10319,15 @@
         <v>19</v>
       </c>
       <c r="AP70" t="s" s="2">
-        <v>374</v>
+        <v>375</v>
       </c>
     </row>
     <row r="71" hidden="true">
       <c r="A71" t="s" s="2">
-        <v>404</v>
+        <v>405</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>376</v>
+        <v>377</v>
       </c>
       <c r="C71" s="2"/>
       <c r="D71" t="s" s="2">
@@ -10349,16 +10353,16 @@
         <v>191</v>
       </c>
       <c r="L71" t="s" s="2">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="M71" t="s" s="2">
-        <v>378</v>
+        <v>379</v>
       </c>
       <c r="N71" t="s" s="2">
-        <v>379</v>
+        <v>380</v>
       </c>
       <c r="O71" t="s" s="2">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="P71" t="s" s="2">
         <v>19</v>
@@ -10407,7 +10411,7 @@
         <v>19</v>
       </c>
       <c r="AF71" t="s" s="2">
-        <v>381</v>
+        <v>382</v>
       </c>
       <c r="AG71" t="s" s="2">
         <v>78</v>
@@ -10428,7 +10432,7 @@
         <v>19</v>
       </c>
       <c r="AM71" t="s" s="2">
-        <v>382</v>
+        <v>383</v>
       </c>
       <c r="AN71" t="s" s="2">
         <v>19</v>
@@ -10437,15 +10441,15 @@
         <v>19</v>
       </c>
       <c r="AP71" t="s" s="2">
-        <v>383</v>
+        <v>384</v>
       </c>
     </row>
     <row r="72" hidden="true">
       <c r="A72" t="s" s="2">
-        <v>405</v>
+        <v>406</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="C72" s="2"/>
       <c r="D72" t="s" s="2">
@@ -10471,16 +10475,16 @@
         <v>161</v>
       </c>
       <c r="L72" t="s" s="2">
-        <v>292</v>
+        <v>293</v>
       </c>
       <c r="M72" t="s" s="2">
-        <v>293</v>
+        <v>294</v>
       </c>
       <c r="N72" t="s" s="2">
-        <v>294</v>
+        <v>295</v>
       </c>
       <c r="O72" t="s" s="2">
-        <v>295</v>
+        <v>296</v>
       </c>
       <c r="P72" t="s" s="2">
         <v>19</v>
@@ -10529,7 +10533,7 @@
         <v>19</v>
       </c>
       <c r="AF72" t="s" s="2">
-        <v>291</v>
+        <v>292</v>
       </c>
       <c r="AG72" t="s" s="2">
         <v>89</v>
@@ -10553,21 +10557,21 @@
         <v>19</v>
       </c>
       <c r="AN72" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO72" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP72" t="s" s="2">
-        <v>298</v>
+        <v>299</v>
       </c>
     </row>
     <row r="73" hidden="true">
       <c r="A73" t="s" s="2">
-        <v>406</v>
+        <v>407</v>
       </c>
       <c r="B73" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="C73" s="2"/>
       <c r="D73" t="s" s="2">
@@ -10593,14 +10597,14 @@
         <v>191</v>
       </c>
       <c r="L73" t="s" s="2">
-        <v>300</v>
+        <v>301</v>
       </c>
       <c r="M73" t="s" s="2">
-        <v>301</v>
+        <v>302</v>
       </c>
       <c r="N73" s="2"/>
       <c r="O73" t="s" s="2">
-        <v>302</v>
+        <v>303</v>
       </c>
       <c r="P73" t="s" s="2">
         <v>19</v>
@@ -10649,7 +10653,7 @@
         <v>19</v>
       </c>
       <c r="AF73" t="s" s="2">
-        <v>299</v>
+        <v>300</v>
       </c>
       <c r="AG73" t="s" s="2">
         <v>78</v>
@@ -10673,21 +10677,21 @@
         <v>19</v>
       </c>
       <c r="AN73" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO73" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP73" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="74" hidden="true">
       <c r="A74" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="B74" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="C74" s="2"/>
       <c r="D74" t="s" s="2">
@@ -10710,17 +10714,17 @@
         <v>90</v>
       </c>
       <c r="K74" t="s" s="2">
-        <v>408</v>
+        <v>409</v>
       </c>
       <c r="L74" t="s" s="2">
-        <v>409</v>
+        <v>410</v>
       </c>
       <c r="M74" t="s" s="2">
-        <v>410</v>
+        <v>411</v>
       </c>
       <c r="N74" s="2"/>
       <c r="O74" t="s" s="2">
-        <v>411</v>
+        <v>412</v>
       </c>
       <c r="P74" t="s" s="2">
         <v>19</v>
@@ -10769,7 +10773,7 @@
         <v>19</v>
       </c>
       <c r="AF74" t="s" s="2">
-        <v>407</v>
+        <v>408</v>
       </c>
       <c r="AG74" t="s" s="2">
         <v>78</v>
@@ -10804,10 +10808,10 @@
     </row>
     <row r="75" hidden="true">
       <c r="A75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="B75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="C75" s="2"/>
       <c r="D75" t="s" s="2">
@@ -10833,14 +10837,14 @@
         <v>191</v>
       </c>
       <c r="L75" t="s" s="2">
-        <v>413</v>
+        <v>414</v>
       </c>
       <c r="M75" t="s" s="2">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="N75" s="2"/>
       <c r="O75" t="s" s="2">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="P75" t="s" s="2">
         <v>19</v>
@@ -10889,7 +10893,7 @@
         <v>19</v>
       </c>
       <c r="AF75" t="s" s="2">
-        <v>412</v>
+        <v>413</v>
       </c>
       <c r="AG75" t="s" s="2">
         <v>78</v>
@@ -10913,7 +10917,7 @@
         <v>19</v>
       </c>
       <c r="AN75" t="s" s="2">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="AO75" t="s" s="2">
         <v>19</v>
@@ -10924,14 +10928,14 @@
     </row>
     <row r="76" hidden="true">
       <c r="A76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="B76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="C76" s="2"/>
       <c r="D76" t="s" s="2">
-        <v>418</v>
+        <v>419</v>
       </c>
       <c r="E76" s="2"/>
       <c r="F76" t="s" s="2">
@@ -10953,16 +10957,16 @@
         <v>187</v>
       </c>
       <c r="L76" t="s" s="2">
-        <v>419</v>
+        <v>420</v>
       </c>
       <c r="M76" t="s" s="2">
-        <v>420</v>
+        <v>421</v>
       </c>
       <c r="N76" t="s" s="2">
-        <v>421</v>
+        <v>422</v>
       </c>
       <c r="O76" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P76" t="s" s="2">
         <v>19</v>
@@ -11011,7 +11015,7 @@
         <v>19</v>
       </c>
       <c r="AF76" t="s" s="2">
-        <v>417</v>
+        <v>418</v>
       </c>
       <c r="AG76" t="s" s="2">
         <v>78</v>
@@ -11046,10 +11050,10 @@
     </row>
     <row r="77" hidden="true">
       <c r="A77" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="B77" t="s" s="2">
-        <v>423</v>
+        <v>424</v>
       </c>
       <c r="C77" s="2"/>
       <c r="D77" t="s" s="2">
@@ -11164,10 +11168,10 @@
     </row>
     <row r="78" hidden="true">
       <c r="A78" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="B78" t="s" s="2">
-        <v>424</v>
+        <v>425</v>
       </c>
       <c r="C78" s="2"/>
       <c r="D78" t="s" s="2">
@@ -11284,10 +11288,10 @@
     </row>
     <row r="79" hidden="true">
       <c r="A79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="B79" t="s" s="2">
-        <v>425</v>
+        <v>426</v>
       </c>
       <c r="C79" s="2"/>
       <c r="D79" t="s" s="2">
@@ -11406,10 +11410,10 @@
     </row>
     <row r="80" hidden="true">
       <c r="A80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="C80" s="2"/>
       <c r="D80" t="s" s="2">
@@ -11435,16 +11439,16 @@
         <v>214</v>
       </c>
       <c r="L80" t="s" s="2">
-        <v>427</v>
+        <v>428</v>
       </c>
       <c r="M80" t="s" s="2">
-        <v>428</v>
+        <v>429</v>
       </c>
       <c r="N80" t="s" s="2">
-        <v>429</v>
+        <v>430</v>
       </c>
       <c r="O80" t="s" s="2">
-        <v>430</v>
+        <v>431</v>
       </c>
       <c r="P80" t="s" s="2">
         <v>19</v>
@@ -11469,13 +11473,13 @@
         <v>19</v>
       </c>
       <c r="X80" t="s" s="2">
-        <v>257</v>
+        <v>258</v>
       </c>
       <c r="Y80" t="s" s="2">
-        <v>431</v>
+        <v>432</v>
       </c>
       <c r="Z80" t="s" s="2">
-        <v>432</v>
+        <v>433</v>
       </c>
       <c r="AA80" t="s" s="2">
         <v>19</v>
@@ -11493,7 +11497,7 @@
         <v>19</v>
       </c>
       <c r="AF80" t="s" s="2">
-        <v>426</v>
+        <v>427</v>
       </c>
       <c r="AG80" t="s" s="2">
         <v>78</v>
@@ -11528,10 +11532,10 @@
     </row>
     <row r="81" hidden="true">
       <c r="A81" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="B81" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="C81" s="2"/>
       <c r="D81" t="s" s="2">
@@ -11557,16 +11561,16 @@
         <v>214</v>
       </c>
       <c r="L81" t="s" s="2">
-        <v>434</v>
+        <v>435</v>
       </c>
       <c r="M81" t="s" s="2">
-        <v>435</v>
+        <v>436</v>
       </c>
       <c r="N81" t="s" s="2">
-        <v>436</v>
+        <v>437</v>
       </c>
       <c r="O81" t="s" s="2">
-        <v>437</v>
+        <v>438</v>
       </c>
       <c r="P81" t="s" s="2">
         <v>19</v>
@@ -11591,11 +11595,11 @@
         <v>19</v>
       </c>
       <c r="X81" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Y81" s="2"/>
       <c r="Z81" t="s" s="2">
-        <v>439</v>
+        <v>440</v>
       </c>
       <c r="AA81" t="s" s="2">
         <v>19</v>
@@ -11613,7 +11617,7 @@
         <v>19</v>
       </c>
       <c r="AF81" t="s" s="2">
-        <v>433</v>
+        <v>434</v>
       </c>
       <c r="AG81" t="s" s="2">
         <v>78</v>
@@ -11648,10 +11652,10 @@
     </row>
     <row r="82" hidden="true">
       <c r="A82" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="B82" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="C82" s="2"/>
       <c r="D82" t="s" s="2">
@@ -11677,14 +11681,14 @@
         <v>214</v>
       </c>
       <c r="L82" t="s" s="2">
-        <v>441</v>
+        <v>442</v>
       </c>
       <c r="M82" t="s" s="2">
-        <v>442</v>
+        <v>443</v>
       </c>
       <c r="N82" s="2"/>
       <c r="O82" t="s" s="2">
-        <v>443</v>
+        <v>444</v>
       </c>
       <c r="P82" t="s" s="2">
         <v>19</v>
@@ -11709,11 +11713,11 @@
         <v>19</v>
       </c>
       <c r="X82" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Y82" s="2"/>
       <c r="Z82" t="s" s="2">
-        <v>444</v>
+        <v>445</v>
       </c>
       <c r="AA82" t="s" s="2">
         <v>19</v>
@@ -11731,7 +11735,7 @@
         <v>19</v>
       </c>
       <c r="AF82" t="s" s="2">
-        <v>440</v>
+        <v>441</v>
       </c>
       <c r="AG82" t="s" s="2">
         <v>78</v>
@@ -11766,10 +11770,10 @@
     </row>
     <row r="83" hidden="true">
       <c r="A83" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="B83" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="C83" s="2"/>
       <c r="D83" t="s" s="2">
@@ -11795,14 +11799,14 @@
         <v>214</v>
       </c>
       <c r="L83" t="s" s="2">
-        <v>446</v>
+        <v>447</v>
       </c>
       <c r="M83" t="s" s="2">
-        <v>447</v>
+        <v>448</v>
       </c>
       <c r="N83" s="2"/>
       <c r="O83" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P83" t="s" s="2">
         <v>19</v>
@@ -11827,11 +11831,11 @@
         <v>19</v>
       </c>
       <c r="X83" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Y83" s="2"/>
       <c r="Z83" t="s" s="2">
-        <v>449</v>
+        <v>450</v>
       </c>
       <c r="AA83" t="s" s="2">
         <v>19</v>
@@ -11849,7 +11853,7 @@
         <v>19</v>
       </c>
       <c r="AF83" t="s" s="2">
-        <v>445</v>
+        <v>446</v>
       </c>
       <c r="AG83" t="s" s="2">
         <v>78</v>
@@ -11884,10 +11888,10 @@
     </row>
     <row r="84" hidden="true">
       <c r="A84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="B84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="C84" s="2"/>
       <c r="D84" t="s" s="2">
@@ -11913,14 +11917,14 @@
         <v>214</v>
       </c>
       <c r="L84" t="s" s="2">
-        <v>451</v>
+        <v>452</v>
       </c>
       <c r="M84" t="s" s="2">
-        <v>452</v>
+        <v>453</v>
       </c>
       <c r="N84" s="2"/>
       <c r="O84" t="s" s="2">
-        <v>448</v>
+        <v>449</v>
       </c>
       <c r="P84" t="s" s="2">
         <v>19</v>
@@ -11945,11 +11949,11 @@
         <v>19</v>
       </c>
       <c r="X84" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Y84" s="2"/>
       <c r="Z84" t="s" s="2">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="AA84" t="s" s="2">
         <v>19</v>
@@ -11967,7 +11971,7 @@
         <v>19</v>
       </c>
       <c r="AF84" t="s" s="2">
-        <v>450</v>
+        <v>451</v>
       </c>
       <c r="AG84" t="s" s="2">
         <v>78</v>
@@ -12002,10 +12006,10 @@
     </row>
     <row r="85" hidden="true">
       <c r="A85" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="C85" s="2"/>
       <c r="D85" t="s" s="2">
@@ -12028,19 +12032,19 @@
         <v>90</v>
       </c>
       <c r="K85" t="s" s="2">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="L85" t="s" s="2">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="M85" t="s" s="2">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="N85" t="s" s="2">
-        <v>458</v>
+        <v>459</v>
       </c>
       <c r="O85" t="s" s="2">
-        <v>459</v>
+        <v>460</v>
       </c>
       <c r="P85" t="s" s="2">
         <v>19</v>
@@ -12089,7 +12093,7 @@
         <v>19</v>
       </c>
       <c r="AF85" t="s" s="2">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="AG85" t="s" s="2">
         <v>78</v>
@@ -12113,21 +12117,21 @@
         <v>19</v>
       </c>
       <c r="AN85" t="s" s="2">
-        <v>296</v>
+        <v>297</v>
       </c>
       <c r="AO85" t="s" s="2">
-        <v>297</v>
+        <v>298</v>
       </c>
       <c r="AP85" t="s" s="2">
-        <v>303</v>
+        <v>304</v>
       </c>
     </row>
     <row r="86" hidden="true">
       <c r="A86" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="C86" s="2"/>
       <c r="D86" t="s" s="2">
@@ -12153,14 +12157,14 @@
         <v>187</v>
       </c>
       <c r="L86" t="s" s="2">
-        <v>461</v>
+        <v>462</v>
       </c>
       <c r="M86" t="s" s="2">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="N86" s="2"/>
       <c r="O86" t="s" s="2">
-        <v>422</v>
+        <v>423</v>
       </c>
       <c r="P86" t="s" s="2">
         <v>19</v>
@@ -12209,7 +12213,7 @@
         <v>19</v>
       </c>
       <c r="AF86" t="s" s="2">
-        <v>460</v>
+        <v>461</v>
       </c>
       <c r="AG86" t="s" s="2">
         <v>78</v>
@@ -12244,10 +12248,10 @@
     </row>
     <row r="87" hidden="true">
       <c r="A87" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="B87" t="s" s="2">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="C87" s="2"/>
       <c r="D87" t="s" s="2">
@@ -12362,10 +12366,10 @@
     </row>
     <row r="88" hidden="true">
       <c r="A88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="B88" t="s" s="2">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="C88" s="2"/>
       <c r="D88" t="s" s="2">
@@ -12482,10 +12486,10 @@
     </row>
     <row r="89" hidden="true">
       <c r="A89" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="B89" t="s" s="2">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C89" s="2"/>
       <c r="D89" t="s" s="2">
@@ -12604,10 +12608,10 @@
     </row>
     <row r="90" hidden="true">
       <c r="A90" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="C90" s="2"/>
       <c r="D90" t="s" s="2">
@@ -12633,14 +12637,14 @@
         <v>214</v>
       </c>
       <c r="L90" t="s" s="2">
-        <v>467</v>
+        <v>468</v>
       </c>
       <c r="M90" t="s" s="2">
-        <v>468</v>
+        <v>469</v>
       </c>
       <c r="N90" s="2"/>
       <c r="O90" t="s" s="2">
-        <v>469</v>
+        <v>470</v>
       </c>
       <c r="P90" t="s" s="2">
         <v>19</v>
@@ -12665,13 +12669,13 @@
         <v>19</v>
       </c>
       <c r="X90" t="s" s="2">
-        <v>438</v>
+        <v>439</v>
       </c>
       <c r="Y90" t="s" s="2">
-        <v>470</v>
+        <v>471</v>
       </c>
       <c r="Z90" t="s" s="2">
-        <v>471</v>
+        <v>472</v>
       </c>
       <c r="AA90" t="s" s="2">
         <v>19</v>
@@ -12689,7 +12693,7 @@
         <v>19</v>
       </c>
       <c r="AF90" t="s" s="2">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="AG90" t="s" s="2">
         <v>89</v>
@@ -12724,10 +12728,10 @@
     </row>
     <row r="91" hidden="true">
       <c r="A91" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="C91" s="2"/>
       <c r="D91" t="s" s="2">
@@ -12750,17 +12754,17 @@
         <v>90</v>
       </c>
       <c r="K91" t="s" s="2">
-        <v>262</v>
+        <v>263</v>
       </c>
       <c r="L91" t="s" s="2">
-        <v>473</v>
+        <v>474</v>
       </c>
       <c r="M91" t="s" s="2">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="N91" s="2"/>
       <c r="O91" t="s" s="2">
-        <v>475</v>
+        <v>476</v>
       </c>
       <c r="P91" t="s" s="2">
         <v>19</v>
@@ -12809,7 +12813,7 @@
         <v>19</v>
       </c>
       <c r="AF91" t="s" s="2">
-        <v>472</v>
+        <v>473</v>
       </c>
       <c r="AG91" t="s" s="2">
         <v>78</v>
@@ -12844,10 +12848,10 @@
     </row>
     <row r="92" hidden="true">
       <c r="A92" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="B92" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="C92" s="2"/>
       <c r="D92" t="s" s="2">
@@ -12870,19 +12874,19 @@
         <v>19</v>
       </c>
       <c r="K92" t="s" s="2">
-        <v>367</v>
+        <v>368</v>
       </c>
       <c r="L92" t="s" s="2">
-        <v>477</v>
+        <v>478</v>
       </c>
       <c r="M92" t="s" s="2">
-        <v>478</v>
+        <v>479</v>
       </c>
       <c r="N92" t="s" s="2">
-        <v>479</v>
+        <v>480</v>
       </c>
       <c r="O92" t="s" s="2">
-        <v>480</v>
+        <v>481</v>
       </c>
       <c r="P92" t="s" s="2">
         <v>19</v>
@@ -12931,7 +12935,7 @@
         <v>19</v>
       </c>
       <c r="AF92" t="s" s="2">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="AG92" t="s" s="2">
         <v>78</v>
@@ -12966,10 +12970,10 @@
     </row>
     <row r="93" hidden="true">
       <c r="A93" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="C93" s="2"/>
       <c r="D93" t="s" s="2">
@@ -12992,17 +12996,17 @@
         <v>19</v>
       </c>
       <c r="K93" t="s" s="2">
-        <v>482</v>
+        <v>483</v>
       </c>
       <c r="L93" t="s" s="2">
-        <v>483</v>
+        <v>484</v>
       </c>
       <c r="M93" t="s" s="2">
-        <v>484</v>
+        <v>485</v>
       </c>
       <c r="N93" s="2"/>
       <c r="O93" t="s" s="2">
-        <v>485</v>
+        <v>486</v>
       </c>
       <c r="P93" t="s" s="2">
         <v>19</v>
@@ -13051,7 +13055,7 @@
         <v>19</v>
       </c>
       <c r="AF93" t="s" s="2">
-        <v>481</v>
+        <v>482</v>
       </c>
       <c r="AG93" t="s" s="2">
         <v>78</v>
@@ -13081,15 +13085,15 @@
         <v>228</v>
       </c>
       <c r="AP93" t="s" s="2">
-        <v>486</v>
+        <v>487</v>
       </c>
     </row>
     <row r="94" hidden="true">
       <c r="A94" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="C94" s="2"/>
       <c r="D94" t="s" s="2">
@@ -13112,17 +13116,17 @@
         <v>19</v>
       </c>
       <c r="K94" t="s" s="2">
-        <v>488</v>
+        <v>489</v>
       </c>
       <c r="L94" t="s" s="2">
-        <v>489</v>
+        <v>490</v>
       </c>
       <c r="M94" t="s" s="2">
-        <v>490</v>
+        <v>491</v>
       </c>
       <c r="N94" s="2"/>
       <c r="O94" t="s" s="2">
-        <v>491</v>
+        <v>492</v>
       </c>
       <c r="P94" t="s" s="2">
         <v>19</v>
@@ -13171,7 +13175,7 @@
         <v>19</v>
       </c>
       <c r="AF94" t="s" s="2">
-        <v>487</v>
+        <v>488</v>
       </c>
       <c r="AG94" t="s" s="2">
         <v>78</v>
